--- a/1-LATEX/2-DADOS/3-OUTPUT/sensibilidade_rho.xlsx
+++ b/1-LATEX/2-DADOS/3-OUTPUT/sensibilidade_rho.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -402,10 +402,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.04486936865596249</v>
+        <v>0.03963900210111772</v>
       </c>
       <c r="D3">
-        <v>0.02121684598240538</v>
+        <v>0.01903144036014725</v>
       </c>
     </row>
     <row r="4">
@@ -418,10 +418,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.0715762333288117</v>
+        <v>0.007406689765167936</v>
       </c>
       <c r="D4">
-        <v>0.02766083366641499</v>
+        <v>0.09260327465062979</v>
       </c>
     </row>
     <row r="5">
@@ -434,10 +434,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.007406689765167936</v>
+        <v>-0.2787297834861159</v>
       </c>
       <c r="D5">
-        <v>0.09260327465062979</v>
+        <v>0.1706084965332423</v>
       </c>
     </row>
     <row r="6">
@@ -450,10 +450,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.2787297834861159</v>
+        <v>0.1716000516464709</v>
       </c>
       <c r="D6">
-        <v>0.1706084965332423</v>
+        <v>0.101150822222562</v>
       </c>
     </row>
     <row r="7">
@@ -466,42 +466,42 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.1716000516464709</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0.101150822222562</v>
+        <v>2.991635273407584E-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>V7</t>
         </is>
       </c>
       <c r="C8">
-        <v>-0.01702358794206319</v>
+        <v>0.05120757691971459</v>
       </c>
       <c r="D8">
-        <v>0.1692918142082444</v>
+        <v>2.050008407799427E-09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="C9">
-        <v>0.04486936865596249</v>
+        <v>0.2796759127099698</v>
       </c>
       <c r="D9">
-        <v>0.02121684598240538</v>
+        <v>4.655057934973063E-10</v>
       </c>
     </row>
     <row r="10">
@@ -510,14 +510,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>V3</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="C10">
-        <v>0.0715762333288117</v>
+        <v>-0.01702358794206319</v>
       </c>
       <c r="D10">
-        <v>0.02766083366641499</v>
+        <v>0.1692918142082444</v>
       </c>
     </row>
     <row r="11">
@@ -526,14 +526,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V2</t>
         </is>
       </c>
       <c r="C11">
-        <v>0.007406689765167936</v>
+        <v>0.03700327186245896</v>
       </c>
       <c r="D11">
-        <v>0.09260327465062979</v>
+        <v>0.01951723453307738</v>
       </c>
     </row>
     <row r="12">
@@ -542,14 +542,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>V5</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="C12">
-        <v>-0.2787297834861159</v>
+        <v>0.007406689765167936</v>
       </c>
       <c r="D12">
-        <v>0.1706084965332423</v>
+        <v>0.09260327465062979</v>
       </c>
     </row>
     <row r="13">
@@ -558,78 +558,78 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>V6</t>
+          <t>V4</t>
         </is>
       </c>
       <c r="C13">
-        <v>0.1716000516464709</v>
+        <v>-0.2787297834861159</v>
       </c>
       <c r="D13">
-        <v>0.101150822222562</v>
+        <v>0.1706084965332423</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>V5</t>
         </is>
       </c>
       <c r="C14">
-        <v>-0.01702358794206319</v>
+        <v>0.1716000516464709</v>
       </c>
       <c r="D14">
-        <v>0.1692918142082444</v>
+        <v>0.101150822222562</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V6</t>
         </is>
       </c>
       <c r="C15">
-        <v>0.04486936865596249</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>0.02121684598240538</v>
+        <v>2.991635273407584E-09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>V3</t>
+          <t>V7</t>
         </is>
       </c>
       <c r="C16">
-        <v>0.0715762333288117</v>
+        <v>0.05120757691971459</v>
       </c>
       <c r="D16">
-        <v>0.02766083366641499</v>
+        <v>2.050008407799427E-09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="C17">
-        <v>0.007406689765167936</v>
+        <v>0.2796759127099698</v>
       </c>
       <c r="D17">
-        <v>0.09260327465062979</v>
+        <v>4.655057934973063E-10</v>
       </c>
     </row>
     <row r="18">
@@ -638,14 +638,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>V5</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="C18">
-        <v>-0.2787297834861159</v>
+        <v>-0.01702358794206319</v>
       </c>
       <c r="D18">
-        <v>0.1706084965332423</v>
+        <v>0.1692918142082444</v>
       </c>
     </row>
     <row r="19">
@@ -654,115 +654,115 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>V6</t>
+          <t>V2</t>
         </is>
       </c>
       <c r="C19">
-        <v>0.1716000516464709</v>
+        <v>0.03117059600999945</v>
       </c>
       <c r="D19">
-        <v>0.101150822222562</v>
+        <v>0.02064469757624502</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="C20">
-        <v>-0.01702358794206319</v>
+        <v>0.007406689765167936</v>
       </c>
       <c r="D20">
-        <v>0.1692918142082444</v>
+        <v>0.09260327465062979</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V4</t>
         </is>
       </c>
       <c r="C21">
-        <v>0.04486936865596249</v>
+        <v>-0.2787297834861159</v>
       </c>
       <c r="D21">
-        <v>0.02121684598240538</v>
+        <v>0.1706084965332423</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>V3</t>
+          <t>V5</t>
         </is>
       </c>
       <c r="C22">
-        <v>0.0715762333288117</v>
+        <v>0.1716000516464709</v>
       </c>
       <c r="D22">
-        <v>0.02766083366641499</v>
+        <v>0.101150822222562</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V6</t>
         </is>
       </c>
       <c r="C23">
-        <v>0.007406689765167936</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0.09260327465062979</v>
+        <v>2.991635273407584E-09</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>V5</t>
+          <t>V7</t>
         </is>
       </c>
       <c r="C24">
-        <v>-0.2787297834861159</v>
+        <v>0.05120757691971459</v>
       </c>
       <c r="D24">
-        <v>0.1706084965332423</v>
+        <v>2.050008407799427E-09</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>V6</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="C25">
-        <v>0.1716000516464709</v>
+        <v>0.2796759127099698</v>
       </c>
       <c r="D25">
-        <v>0.101150822222562</v>
+        <v>4.655057934973063E-10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -786,15 +786,15 @@
         </is>
       </c>
       <c r="C27">
-        <v>0.04486936865596249</v>
+        <v>0.01655094282820235</v>
       </c>
       <c r="D27">
-        <v>0.02121684598240538</v>
+        <v>0.02389601709455585</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -802,15 +802,15 @@
         </is>
       </c>
       <c r="C28">
-        <v>0.0715762333288117</v>
+        <v>0.007406689765167936</v>
       </c>
       <c r="D28">
-        <v>0.02766083366641499</v>
+        <v>0.09260327465062979</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -818,15 +818,15 @@
         </is>
       </c>
       <c r="C29">
-        <v>0.007406689765167936</v>
+        <v>-0.2787297834861159</v>
       </c>
       <c r="D29">
-        <v>0.09260327465062979</v>
+        <v>0.1706084965332423</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -834,15 +834,15 @@
         </is>
       </c>
       <c r="C30">
-        <v>-0.2787297834861159</v>
+        <v>0.1716000516464709</v>
       </c>
       <c r="D30">
-        <v>0.1706084965332423</v>
+        <v>0.101150822222562</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -850,106 +850,298 @@
         </is>
       </c>
       <c r="C31">
-        <v>0.1716000516464709</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>0.101150822222562</v>
+        <v>2.991635273407584E-09</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>V7</t>
         </is>
       </c>
       <c r="C32">
-        <v>-0.01702358794206319</v>
+        <v>0.05120757691971459</v>
       </c>
       <c r="D32">
-        <v>0.1692918142082444</v>
+        <v>2.050008407799427E-09</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="C33">
-        <v>0.04486936865596249</v>
+        <v>0.2796759127099698</v>
       </c>
       <c r="D33">
-        <v>0.02121684598240538</v>
+        <v>4.655057934973063E-10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>V3</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="C34">
-        <v>0.0715762333288117</v>
+        <v>-0.01702358794206319</v>
       </c>
       <c r="D34">
-        <v>0.02766083366641499</v>
+        <v>0.1692918142082444</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V2</t>
         </is>
       </c>
       <c r="C35">
-        <v>0.007406689765167936</v>
+        <v>-0.04424600487697795</v>
       </c>
       <c r="D35">
-        <v>0.09260327465062979</v>
+        <v>0.04279123217496131</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>V5</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="C36">
-        <v>-0.2787297834861159</v>
+        <v>0.007406689765167936</v>
       </c>
       <c r="D36">
-        <v>0.1706084965332423</v>
+        <v>0.09260327465062979</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
+        <v>0.9</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>V4</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>-0.2787297834861159</v>
+      </c>
+      <c r="D37">
+        <v>0.1706084965332423</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.9</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>0.1716000516464709</v>
+      </c>
+      <c r="D38">
+        <v>0.101150822222562</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.9</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>2.991635273407584E-09</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.9</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>0.05120757691971459</v>
+      </c>
+      <c r="D40">
+        <v>2.050008407799427E-09</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.9</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>0.2796759127099698</v>
+      </c>
+      <c r="D41">
+        <v>4.655057934973063E-10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
         <v>1</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>-0.01702358794206319</v>
+      </c>
+      <c r="D42">
+        <v>0.1692918142082444</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>1</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>-0.3849170047775033</v>
+      </c>
+      <c r="D43">
+        <v>0.2033886512861532</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>1</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>0.007406689765167936</v>
+      </c>
+      <c r="D44">
+        <v>0.09260327465062979</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>1</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>V4</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>-0.2787297834861159</v>
+      </c>
+      <c r="D45">
+        <v>0.1706084965332423</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>1</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>0.1716000516464709</v>
+      </c>
+      <c r="D46">
+        <v>0.101150822222562</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>1</v>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>V6</t>
         </is>
       </c>
-      <c r="C37">
-        <v>0.1716000516464709</v>
-      </c>
-      <c r="D37">
-        <v>0.101150822222562</v>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>2.991635273407584E-09</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>1</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>0.05120757691971459</v>
+      </c>
+      <c r="D48">
+        <v>2.050008407799427E-09</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>1</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>0.2796759127099698</v>
+      </c>
+      <c r="D49">
+        <v>4.655057934973063E-10</v>
       </c>
     </row>
   </sheetData>
